--- a/processed_category2_values.xlsx
+++ b/processed_category2_values.xlsx
@@ -469,12 +469,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -791,58 +791,58 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y2轴(数控)/徐州格迪电机轴</t>
+          <t>Y2轴(数控)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Y2ZSKXZGDDJZ</t>
+          <t>Y2ZSK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y2轴(普车)/徐州格迪电机轴</t>
+          <t>Y2轴(普车)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Y2ZPCXZGDDJZ</t>
+          <t>Y2ZPC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2539,12 +2539,12 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2585,12 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:01</t>
+          <t>2026-02-03 11:14:10</t>
         </is>
       </c>
     </row>
